--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484851_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484851_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6621</v>
+        <v>4.0493</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7284</v>
+        <v>4.2743</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0663</v>
+        <v>-0.225</v>
       </c>
       <c r="G2" t="n">
         <v>1.8457</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8512</v>
+        <v>-0.4639</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2933</v>
+        <v>-0.7474</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4421</v>
+        <v>0.2834</v>
       </c>
       <c r="V2" t="n">
         <v>3.7998</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. LOPEZ RICO</t>
+          <t>V. VICENT TORTOSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7097</v>
+        <v>3.04</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6496</v>
+        <v>4.1869</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0601</v>
+        <v>-1.1469</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6529</v>
+        <v>4.268</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1809</v>
+        <v>0.2348</v>
       </c>
       <c r="I3" t="n">
-        <v>0.472</v>
+        <v>4.0333</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1176</v>
+        <v>5.3795</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0354</v>
+        <v>1.3899</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0823</v>
+        <v>3.9896</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5353</v>
+        <v>-1.1114</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1456</v>
+        <v>-1.1551</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3897</v>
+        <v>0.0437</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5473</v>
+        <v>-1.228</v>
       </c>
       <c r="T3" t="n">
-        <v>0.532</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0153</v>
+        <v>-0.6771</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3208</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. VICENT TORTOSA</t>
+          <t>M. LOPEZ RICO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3211</v>
+        <v>2.2406</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6796</v>
+        <v>1.2599</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3585</v>
+        <v>0.9808</v>
       </c>
       <c r="G4" t="n">
-        <v>4.268</v>
+        <v>1.6529</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2348</v>
+        <v>1.1809</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0333</v>
+        <v>0.472</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3795</v>
+        <v>1.1176</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3899</v>
+        <v>1.0354</v>
       </c>
       <c r="L4" t="n">
-        <v>3.9896</v>
+        <v>0.0823</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1114</v>
+        <v>0.5353</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1551</v>
+        <v>0.1456</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0437</v>
+        <v>0.3897</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9469</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0582</v>
+        <v>0.1422</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8888</v>
+        <v>-0.064</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3018</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4605</v>
+        <v>2.0833</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6459</v>
+        <v>2.3481</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1854</v>
+        <v>-0.2647</v>
       </c>
       <c r="G5" t="n">
         <v>1.8005</v>
@@ -844,13 +844,13 @@
         <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6684</v>
+        <v>-0.0455</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0582</v>
+        <v>-0.356</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3898</v>
+        <v>0.3105</v>
       </c>
       <c r="V5" t="n">
         <v>0.7057</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8206</v>
+        <v>-0.6321</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5545</v>
+        <v>-0.3395</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2661</v>
+        <v>-0.2926</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5433</v>
@@ -922,13 +922,13 @@
         <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8436</v>
+        <v>-0.655</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.6051</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0234</v>
+        <v>-0.0499</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3208</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2934</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6319</v>
+        <v>2.0217</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9254</v>
+        <v>-2.8196</v>
       </c>
       <c r="G7" t="n">
         <v>2.9754</v>
@@ -1000,13 +1000,13 @@
         <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0052</v>
+        <v>-1.5096</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.117</v>
+        <v>-0.7272</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8882</v>
+        <v>-0.7824</v>
       </c>
       <c r="V7" t="n">
         <v>-3.3958</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0202</v>
+        <v>-1.675</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7421</v>
+        <v>-0.4498</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2782</v>
+        <v>-1.2253</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0043</v>
@@ -1078,13 +1078,13 @@
         <v>0.3774</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1557</v>
+        <v>-0.8105</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5291</v>
+        <v>-0.2368</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6266</v>
+        <v>-0.5737</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2377</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2885</v>
+        <v>-3.3452</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1694</v>
+        <v>-1.3055</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.119</v>
+        <v>-2.0397</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3945</v>
@@ -1156,13 +1156,13 @@
         <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2904</v>
+        <v>-0.3471</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2323</v>
+        <v>-0.3683</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0581</v>
+        <v>0.0212</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6036</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.403</v>
+        <v>-5.7936</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8042</v>
+        <v>-3.1683</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5988</v>
+        <v>-2.6253</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2409</v>
@@ -1234,13 +1234,13 @@
         <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9999</v>
+        <v>-0.3906</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4225</v>
+        <v>0.0584</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4226</v>
+        <v>-0.4491</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7847</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2782</v>
+        <v>-6.5323</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5911</v>
+        <v>-4.7658</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6871</v>
+        <v>-1.7664</v>
       </c>
       <c r="G11" t="n">
         <v>-6.071</v>
@@ -1312,13 +1312,13 @@
         <v>2.0757</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1016</v>
+        <v>-1.3557</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5821</v>
+        <v>-0.7568</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5196</v>
+        <v>-0.5989</v>
       </c>
       <c r="V11" t="n">
         <v>0.7057</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.950499999999998</v>
+        <v>-7.362900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.474100000000001</v>
+        <v>4.062</v>
       </c>
       <c r="F12" t="n">
         <v>-11.4247</v>
@@ -1390,13 +1390,13 @@
         <v>12.2655</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.315799999999999</v>
+        <v>-6.7277</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.735799999999999</v>
+        <v>-4.1479</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.5801</v>
+        <v>-2.58</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8106000000000002</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.1065</v>
+        <v>5.0281</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6249</v>
+        <v>3.2608</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4816</v>
+        <v>1.7673</v>
       </c>
       <c r="G13" t="n">
         <v>2.0216</v>
@@ -1468,13 +1468,13 @@
         <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1796</v>
+        <v>2.1013</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1432</v>
+        <v>0.7791</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0365</v>
+        <v>1.3222</v>
       </c>
       <c r="V13" t="n">
         <v>2.7922</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4184</v>
+        <v>4.371</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6327</v>
+        <v>3.2943</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7857</v>
+        <v>1.0767</v>
       </c>
       <c r="G14" t="n">
         <v>1.0762</v>
@@ -1546,13 +1546,13 @@
         <v>0.9435</v>
       </c>
       <c r="S14" t="n">
-        <v>4.116</v>
+        <v>2.0686</v>
       </c>
       <c r="T14" t="n">
-        <v>4.0178</v>
+        <v>1.6794</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0982</v>
+        <v>0.3892</v>
       </c>
       <c r="V14" t="n">
         <v>1.2262</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9753</v>
+        <v>3.3478</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0994</v>
+        <v>2.366</v>
       </c>
       <c r="F16" t="n">
-        <v>0.876</v>
+        <v>0.9818</v>
       </c>
       <c r="G16" t="n">
         <v>0.7324000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8512</v>
+        <v>0.5213</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.281</v>
+        <v>-0.0143</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4298</v>
+        <v>0.5356</v>
       </c>
       <c r="V16" t="n">
         <v>1.528</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7989</v>
+        <v>2.1177</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4356</v>
+        <v>2.7279</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6367</v>
+        <v>-0.6102</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5766</v>
@@ -1780,13 +1780,13 @@
         <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9981</v>
+        <v>1.3169</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3585</v>
+        <v>0.6508</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6661</v>
       </c>
       <c r="V17" t="n">
         <v>0.6226</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7396</v>
+        <v>0.6412</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7832</v>
+        <v>0.386</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0436</v>
+        <v>0.2552</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2855</v>
@@ -1858,13 +1858,13 @@
         <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5673</v>
+        <v>0.8136</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2222</v>
+        <v>-0.053</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6549</v>
+        <v>0.8666</v>
       </c>
       <c r="V18" t="n">
         <v>0.9244</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2325</v>
+        <v>-0.6097</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2624</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0299</v>
+        <v>-1.1515</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4604</v>
+        <v>1.2593</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5642</v>
+        <v>1.2091</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1038</v>
+        <v>0.0502</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0382</v>
+        <v>3.0909</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0211</v>
+        <v>2.2187</v>
       </c>
       <c r="L19" t="n">
-        <v>0.017</v>
+        <v>0.8723</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4986</v>
+        <v>-1.8316</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5854</v>
+        <v>-1.0095</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0868</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1887</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3192</v>
+        <v>0.7726</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4703</v>
+        <v>0.1682</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1511</v>
+        <v>0.6044</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-1.8868</v>
       </c>
       <c r="W19" t="n">
         <v>-0.6415999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.424</v>
+        <v>-1.2938</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1402</v>
+        <v>-1.165</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2838</v>
+        <v>-0.1288</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2593</v>
+        <v>-0.4604</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2091</v>
+        <v>-0.5642</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0502</v>
+        <v>0.1038</v>
       </c>
       <c r="J20" t="n">
-        <v>3.0909</v>
+        <v>0.0382</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2187</v>
+        <v>0.0211</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8723</v>
+        <v>0.017</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8316</v>
+        <v>-0.4986</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0095</v>
+        <v>-0.5854</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8221000000000001</v>
+        <v>0.0868</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3209</v>
+        <v>0.3774</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0417</v>
+        <v>-0.3805</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5139</v>
+        <v>-0.3729</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4721</v>
+        <v>-0.0076</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8868</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W20" t="n">
         <v>-0.6415999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4774</v>
+        <v>-4.3883</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0204</v>
+        <v>-0.8256</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4569</v>
+        <v>-3.5628</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2814</v>
@@ -2092,13 +2092,13 @@
         <v>0.1887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4603</v>
+        <v>-0.3712</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.4518</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1864</v>
+        <v>0.0806</v>
       </c>
       <c r="V21" t="n">
         <v>-2.7922</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9108</v>
+        <v>-4.6991</v>
       </c>
       <c r="E22" t="n">
         <v>-2.5972</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3136</v>
+        <v>-2.102</v>
       </c>
       <c r="G22" t="n">
         <v>-4.21</v>
@@ -2170,13 +2170,13 @@
         <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2616</v>
+        <v>0.4732</v>
       </c>
       <c r="T22" t="n">
         <v>0.1945</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.2787</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9624</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.9504</v>
+        <v>7.9505</v>
       </c>
       <c r="E23" t="n">
-        <v>11.4248</v>
+        <v>11.4246</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4742</v>
+        <v>-3.4743</v>
       </c>
       <c r="G23" t="n">
         <v>1.711200000000001</v>
@@ -2248,13 +2248,13 @@
         <v>10.3785</v>
       </c>
       <c r="S23" t="n">
-        <v>7.315599999999999</v>
+        <v>7.315800000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>2.579900000000001</v>
+        <v>2.58</v>
       </c>
       <c r="U23" t="n">
-        <v>4.7357</v>
+        <v>4.7358</v>
       </c>
       <c r="V23" t="n">
         <v>0.8104000000000006</v>
